--- a/attachments/DSJ_AE_AI_and_DataBusiness_Analytics_Methodologies_and_Applications.xlsx
+++ b/attachments/DSJ_AE_AI_and_DataBusiness_Analytics_Methodologies_and_Applications.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_7E9A717F_8565_4B7E_B2E7_96165FD3A5DC_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$44</definedName>
+    <definedName name="Z_7E9A717F_8565_4B7E_B2E7_96165FD3A5DC_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$45</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
   <customWorkbookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="178">
   <si>
     <t>First Name</t>
   </si>
@@ -404,6 +404,21 @@
   </si>
   <si>
     <t>The Ohio State University</t>
+  </si>
+  <si>
+    <t>Shaokun</t>
+  </si>
+  <si>
+    <t>Fan</t>
+  </si>
+  <si>
+    <t>fans@oregonstate.edu</t>
+  </si>
+  <si>
+    <t>College of Business</t>
+  </si>
+  <si>
+    <t>Oregon State University</t>
   </si>
   <si>
     <t>DSJ Editorial Review Board Members</t>
@@ -549,12 +564,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -577,12 +592,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -595,18 +604,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -619,7 +634,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -628,13 +658,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -650,22 +673,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -689,14 +696,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -709,8 +724,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -723,21 +747,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -760,7 +769,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +793,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,13 +895,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,31 +919,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -838,43 +937,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -886,61 +949,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -982,46 +991,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1042,16 +1012,40 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1066,159 +1060,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1226,11 +1234,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1497,7 +1505,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L997"/>
+  <dimension ref="A1:L998"/>
   <sheetFormatPr defaultColWidth="12.6071428571429" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -2000,7 +2008,7 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2029,7 +2037,7 @@
       <c r="C16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>125</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -2039,61 +2047,43 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:1">
-      <c r="A17" s="2" t="s">
+    <row r="17" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:5">
+      <c r="A17" s="1" t="s">
         <v>127</v>
       </c>
+      <c r="B17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="1" t="s">
+    <row r="18" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:1">
+      <c r="A18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="1" t="s">
+    </row>
+    <row r="19" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:11">
+      <c r="A19" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>18</v>
@@ -2102,36 +2092,33 @@
         <v>20</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A20" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="D20" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -2140,33 +2127,36 @@
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:11">
+      <c r="A21" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
@@ -2175,36 +2165,33 @@
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
       <c r="A22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>18</v>
@@ -2213,122 +2200,159 @@
         <v>20</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
       <c r="A23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="L23" s="1" t="s">
+      <c r="I24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="15.75" customHeight="1"/>
     <row r="25" s="1" customFormat="1" ht="15.75" customHeight="1"/>
     <row r="26" s="1" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1" spans="3:12">
-      <c r="C28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
+    <row r="27" s="1" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1" spans="3:12">
+      <c r="C29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:12">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+    </row>
     <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1" spans="10:10">
-      <c r="J34" s="10"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1" spans="10:10">
+      <c r="J35" s="9"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
@@ -2337,20 +2361,20 @@
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1" spans="1:11">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1" spans="1:11">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1"/>
     <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
@@ -3303,6 +3327,7 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{7E9A717F-8565-4B7E-B2E7-96165FD3A5DC}" filter="1" showAutoFilter="1">
@@ -3312,13 +3337,14 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="2">
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="K45:L45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" display="makturk@clemson.edu"/>
     <hyperlink ref="C7" r:id="rId2" display="ycsong@umn.edu "/>
     <hyperlink ref="C16" r:id="rId3" display="qili.wang@fisher.osu.edu"/>
+    <hyperlink ref="C17" r:id="rId4" display="fans@oregonstate.edu"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
